--- a/PATXOT 512/Octubre/PATXOT 521 Octubre.xlsx
+++ b/PATXOT 512/Octubre/PATXOT 521 Octubre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PATXOT 512\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PATXOT 512\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F43BF9B-6BDA-412C-863E-4C84D8004346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C59A0F-B9B3-40C3-8782-64B7524940F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -428,19 +428,19 @@
     <t>EDESUR:</t>
   </si>
   <si>
-    <t>LIQUIDACIÓN EXPENSAS septiembre 2025</t>
-  </si>
-  <si>
-    <t>AYSA - septiembre</t>
-  </si>
-  <si>
-    <t>Honorarios Administracion - septiembre</t>
-  </si>
-  <si>
-    <t>Poliza de Seguro Obligatoria Mercantil andina N. 1181593 - septiembre</t>
-  </si>
-  <si>
-    <t>Edesur - septiembre</t>
+    <t>LIQUIDACIÓN EXPENSAS OCTUBRE 2025</t>
+  </si>
+  <si>
+    <t>AYSA - OCTUBRE</t>
+  </si>
+  <si>
+    <t>Honorarios Administracion - OCTUBRE</t>
+  </si>
+  <si>
+    <t>Poliza de Seguro Obligatoria Mercantil andina N. 1181593 - OCTUBRE</t>
+  </si>
+  <si>
+    <t>Edesur - OCTUBRE</t>
   </si>
 </sst>
 </file>
@@ -1754,28 +1754,16 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1794,6 +1782,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2196,16 +2196,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:F52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>21</v>
       </c>
@@ -2213,66 +2213,66 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="25"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="169" t="s">
         <v>132</v>
       </c>
       <c r="B7" s="26"/>
       <c r="C7" s="26"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="23" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="86" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="75"/>
       <c r="C16" s="11"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="75" t="s">
         <v>133</v>
       </c>
@@ -2280,27 +2280,27 @@
         <v>62</v>
       </c>
       <c r="C17" s="174">
-        <v>91854.86</v>
+        <v>91854.55</v>
       </c>
       <c r="D17" s="48"/>
       <c r="F17" s="14"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="88"/>
       <c r="B18" s="89"/>
       <c r="C18" s="60">
         <f>SUM(C17:C17)</f>
-        <v>91854.86</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>91854.55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="86" t="s">
         <v>35</v>
       </c>
       <c r="B19" s="87"/>
       <c r="C19" s="90"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="75" t="s">
         <v>134</v>
       </c>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="F20" s="22"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="75" t="s">
         <v>135</v>
       </c>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="F21" s="22"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="75" t="s">
         <v>124</v>
       </c>
@@ -2330,7 +2330,7 @@
       <c r="E22" s="14"/>
       <c r="F22" s="22"/>
     </row>
-    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="88"/>
       <c r="B23" s="89"/>
       <c r="C23" s="60">
@@ -2339,51 +2339,51 @@
       </c>
       <c r="F23" s="22"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="79" t="s">
         <v>78</v>
       </c>
       <c r="B24" s="79"/>
       <c r="C24" s="92">
         <f>+C23+C18</f>
-        <v>165389.46000000002</v>
+        <v>165389.15000000002</v>
       </c>
       <c r="F24" s="22"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C25" s="61"/>
       <c r="F25" s="22"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="23" t="s">
         <v>43</v>
       </c>
       <c r="C26" s="61"/>
       <c r="F26" s="22"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="75"/>
       <c r="B27" s="75"/>
       <c r="C27" s="84"/>
       <c r="F27" s="22"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="75"/>
       <c r="B28" s="75"/>
       <c r="C28" s="85"/>
       <c r="F28" s="22"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="75"/>
       <c r="B29" s="75"/>
       <c r="C29" s="85"/>
       <c r="F29" s="22"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C30" s="63"/>
       <c r="F30" s="22"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="23" t="s">
         <v>40</v>
       </c>
@@ -2394,93 +2394,93 @@
       </c>
       <c r="E31" s="14"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="34" t="s">
         <v>15</v>
       </c>
       <c r="B33" s="34"/>
       <c r="C33" s="35">
         <f>+C31+C24</f>
-        <v>165389.46000000002</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="35" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>165389.15000000002</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="146" t="s">
         <v>36</v>
       </c>
       <c r="B35" s="147"/>
       <c r="C35" s="148"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="144" t="s">
         <v>10</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="145">
-        <v>-406759.6</v>
+        <v>-801914.71</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="32">
         <f>'prorrateo '!F15</f>
-        <v>0</v>
+        <v>478447.75360000005</v>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>136</v>
       </c>
       <c r="C38" s="93">
-        <v>-229765.65</v>
+        <v>-239356.26</v>
       </c>
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>64</v>
       </c>
       <c r="C39" s="93">
         <f>-(C24-C22)</f>
-        <v>-165389.46000000002</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+        <v>-165389.15000000002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="36" t="s">
         <v>16</v>
       </c>
       <c r="B40" s="33"/>
       <c r="C40" s="40">
         <f>SUM(C36:C39)</f>
-        <v>-801914.71</v>
+        <v>-728212.36639999994</v>
       </c>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="19"/>
       <c r="B41" s="18"/>
       <c r="C41" s="20"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="19"/>
       <c r="B42" s="18"/>
       <c r="C42" s="20"/>
       <c r="F42" s="94"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="19"/>
       <c r="B43" s="18"/>
       <c r="C43" s="20"/>
     </row>
-    <row r="44" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="73" t="s">
         <v>57</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="75" t="s">
         <v>63</v>
       </c>
@@ -2499,17 +2499,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="75"/>
       <c r="B46" s="75"/>
       <c r="C46" s="82"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="75"/>
       <c r="B47" s="75"/>
       <c r="C47" s="83"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="79" t="s">
         <v>4</v>
       </c>
@@ -2519,22 +2519,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="18"/>
       <c r="B49" s="18"/>
       <c r="C49" s="18"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="18"/>
       <c r="B50" s="18"/>
       <c r="C50" s="18"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="18"/>
       <c r="B51" s="18"/>
       <c r="C51" s="18"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="18"/>
       <c r="B52" s="18"/>
       <c r="C52" s="18"/>
@@ -2556,37 +2556,39 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N128"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="4" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" customWidth="1"/>
-    <col min="9" max="9" width="8.28515625" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" style="21"/>
+    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.44140625" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.44140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="52" t="s">
         <v>48</v>
       </c>
       <c r="E1" s="14">
-        <v>165389.46000000002</v>
+        <v>165389.15000000002</v>
       </c>
       <c r="H1" s="175" t="s">
         <v>131</v>
       </c>
       <c r="I1" s="175"/>
-      <c r="J1" s="14"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J1" s="14">
+        <v>239356.26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="97">
         <f>'detalle y gastos'!B7</f>
         <v>0</v>
@@ -2603,15 +2605,15 @@
       <c r="K2" s="101"/>
       <c r="L2" s="102"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="199" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="195" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="200"/>
-      <c r="C3" s="189" t="s">
+      <c r="B3" s="196"/>
+      <c r="C3" s="191" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="197" t="s">
+      <c r="D3" s="193" t="s">
         <v>55</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -2620,89 +2622,92 @@
       <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="189" t="s">
+      <c r="G3" s="191" t="s">
         <v>53</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="195" t="s">
+      <c r="I3" s="201" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="191" t="s">
+      <c r="J3" s="199" t="s">
         <v>110</v>
       </c>
-      <c r="K3" s="189" t="s">
+      <c r="K3" s="191" t="s">
         <v>42</v>
       </c>
       <c r="L3" s="45" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="201"/>
-      <c r="B4" s="202"/>
-      <c r="C4" s="190"/>
-      <c r="D4" s="198"/>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="197"/>
+      <c r="B4" s="198"/>
+      <c r="C4" s="192"/>
+      <c r="D4" s="194"/>
       <c r="E4" s="57" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="190"/>
+      <c r="G4" s="192"/>
       <c r="H4" s="37">
         <v>0.04</v>
       </c>
-      <c r="I4" s="196"/>
-      <c r="J4" s="192"/>
-      <c r="K4" s="190"/>
+      <c r="I4" s="202"/>
+      <c r="J4" s="200"/>
+      <c r="K4" s="192"/>
       <c r="L4" s="38" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="193">
+    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="189">
         <v>1</v>
       </c>
-      <c r="B5" s="194"/>
+      <c r="B5" s="190"/>
       <c r="C5" s="110" t="s">
         <v>65</v>
       </c>
       <c r="D5" s="58"/>
       <c r="E5" s="149">
-        <v>41531.40466575251</v>
-      </c>
-      <c r="F5" s="150"/>
+        <v>66016.406332382612</v>
+      </c>
+      <c r="F5" s="150">
+        <f>E5</f>
+        <v>66016.406332382612</v>
+      </c>
       <c r="G5" s="151">
         <f>E5-F5</f>
-        <v>41531.40466575251</v>
+        <v>0</v>
       </c>
       <c r="H5" s="151">
         <f>IF(G5&gt;0,G5*4%,0)</f>
-        <v>1661.2561866301005</v>
+        <v>0</v>
       </c>
       <c r="I5" s="95">
         <v>13.8</v>
       </c>
       <c r="J5" s="96">
         <f>E$1*I5/100</f>
-        <v>22823.745480000005</v>
+        <v>22823.702700000005</v>
       </c>
       <c r="K5" s="142">
         <f>J$1*I5/100</f>
-        <v>0</v>
+        <v>33031.16388</v>
       </c>
       <c r="L5" s="103">
         <f>G5+H5+J5+K5</f>
-        <v>66016.406332382612</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="193">
+        <v>55854.866580000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="27" x14ac:dyDescent="0.3">
+      <c r="A6" s="189">
         <v>2</v>
       </c>
-      <c r="B6" s="194"/>
+      <c r="B6" s="190"/>
       <c r="C6" s="110" t="s">
         <v>66</v>
       </c>
@@ -2710,38 +2715,41 @@
         <v>71</v>
       </c>
       <c r="E6" s="149">
-        <v>36166.928390240799</v>
-      </c>
-      <c r="F6" s="150"/>
+        <v>57228.795481850429</v>
+      </c>
+      <c r="F6" s="150">
+        <f t="shared" ref="F6:F14" si="0">E6</f>
+        <v>57228.795481850429</v>
+      </c>
       <c r="G6" s="151">
-        <f t="shared" ref="G6:G14" si="0">E6-F6</f>
-        <v>36166.928390240799</v>
+        <f t="shared" ref="G6:G14" si="1">E6-F6</f>
+        <v>0</v>
       </c>
       <c r="H6" s="151">
-        <f t="shared" ref="H6:H14" si="1">IF(G6&gt;0,G6*4%,0)</f>
-        <v>1446.6771356096319</v>
+        <f t="shared" ref="H6:H14" si="2">IF(G6&gt;0,G6*4%,0)</f>
+        <v>0</v>
       </c>
       <c r="I6" s="95">
         <v>11.86</v>
       </c>
       <c r="J6" s="96">
-        <f t="shared" ref="J6:J14" si="2">E$1*I6/100</f>
-        <v>19615.189956000002</v>
+        <f t="shared" ref="J6:J14" si="3">E$1*I6/100</f>
+        <v>19615.153190000001</v>
       </c>
       <c r="K6" s="142">
-        <f t="shared" ref="K6:K14" si="3">J$1*I6/100</f>
-        <v>0</v>
+        <f t="shared" ref="K6:K14" si="4">J$1*I6/100</f>
+        <v>28387.652436</v>
       </c>
       <c r="L6" s="103">
-        <f t="shared" ref="L6:L14" si="4">G6+H6+J6+K6</f>
-        <v>57228.795481850429</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="193">
+        <f t="shared" ref="L6:L14" si="5">G6+H6+J6+K6</f>
+        <v>48002.805626000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="27" x14ac:dyDescent="0.3">
+      <c r="A7" s="189">
         <v>3</v>
       </c>
-      <c r="B7" s="194"/>
+      <c r="B7" s="190"/>
       <c r="C7" s="110" t="s">
         <v>66</v>
       </c>
@@ -2749,38 +2757,41 @@
         <v>72</v>
       </c>
       <c r="E7" s="149">
-        <v>37894.033173585289</v>
-      </c>
-      <c r="F7" s="150"/>
+        <v>60017.321216528711</v>
+      </c>
+      <c r="F7" s="150">
+        <f t="shared" si="0"/>
+        <v>60017.321216528711</v>
+      </c>
       <c r="G7" s="151">
-        <f t="shared" si="0"/>
-        <v>37894.033173585289</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H7" s="151">
-        <f t="shared" si="1"/>
-        <v>1515.7613269434116</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I7" s="95">
         <v>12.46</v>
       </c>
       <c r="J7" s="96">
-        <f t="shared" si="2"/>
-        <v>20607.526716000004</v>
+        <f t="shared" si="3"/>
+        <v>20607.488090000003</v>
       </c>
       <c r="K7" s="142">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>29823.789996000003</v>
       </c>
       <c r="L7" s="103">
-        <f t="shared" si="4"/>
-        <v>60017.321216528711</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="193">
+        <f t="shared" si="5"/>
+        <v>50431.278086000006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="189">
         <v>4</v>
       </c>
-      <c r="B8" s="194"/>
+      <c r="B8" s="190"/>
       <c r="C8" s="110" t="s">
         <v>67</v>
       </c>
@@ -2788,38 +2799,41 @@
         <v>73</v>
       </c>
       <c r="E8" s="149">
-        <v>44723.725567140471</v>
-      </c>
-      <c r="F8" s="150"/>
+        <v>70907.619939826094</v>
+      </c>
+      <c r="F8" s="150">
+        <f t="shared" si="0"/>
+        <v>70907.619939826094</v>
+      </c>
       <c r="G8" s="151">
-        <f t="shared" si="0"/>
-        <v>44723.725567140471</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H8" s="151">
-        <f t="shared" si="1"/>
-        <v>1788.949022685619</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I8" s="95">
         <v>14.75</v>
       </c>
       <c r="J8" s="96">
-        <f t="shared" si="2"/>
-        <v>24394.945350000002</v>
+        <f t="shared" si="3"/>
+        <v>24394.899625000005</v>
       </c>
       <c r="K8" s="142">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>35305.048349999997</v>
       </c>
       <c r="L8" s="103">
-        <f t="shared" si="4"/>
-        <v>70907.619939826094</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="193">
+        <f t="shared" si="5"/>
+        <v>59699.947975000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="189">
         <v>5</v>
       </c>
-      <c r="B9" s="194"/>
+      <c r="B9" s="190"/>
       <c r="C9" s="110" t="s">
         <v>68</v>
       </c>
@@ -2827,222 +2841,240 @@
         <v>74</v>
       </c>
       <c r="E9" s="149">
-        <v>37111.569982331108</v>
-      </c>
-      <c r="F9" s="150"/>
+        <v>59120.864767624356</v>
+      </c>
+      <c r="F9" s="150">
+        <f t="shared" si="0"/>
+        <v>59120.864767624356</v>
+      </c>
       <c r="G9" s="151">
-        <f t="shared" si="0"/>
-        <v>37111.569982331108</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H9" s="151">
-        <f t="shared" si="1"/>
-        <v>1484.4627992932444</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I9" s="95">
         <v>12.41</v>
       </c>
       <c r="J9" s="96">
-        <f t="shared" si="2"/>
-        <v>20524.831986000001</v>
+        <f t="shared" si="3"/>
+        <v>20524.793515000005</v>
       </c>
       <c r="K9" s="142">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>29704.111866000003</v>
       </c>
       <c r="L9" s="103">
         <f>G9+H9+J9+K9</f>
-        <v>59120.864767624356</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="193">
+        <v>50228.905381000004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="189">
         <v>6</v>
       </c>
-      <c r="B10" s="194"/>
+      <c r="B10" s="190"/>
       <c r="C10" s="110" t="s">
         <v>69</v>
       </c>
       <c r="D10" s="72"/>
       <c r="E10" s="149">
-        <v>37332.293419986621</v>
-      </c>
-      <c r="F10" s="150"/>
+        <v>59466.18976478609</v>
+      </c>
+      <c r="F10" s="150">
+        <f t="shared" si="0"/>
+        <v>59466.18976478609</v>
+      </c>
       <c r="G10" s="151">
-        <f t="shared" si="0"/>
-        <v>37332.293419986621</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H10" s="151">
-        <f t="shared" si="1"/>
-        <v>1493.2917367994648</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I10" s="95">
         <v>12.48</v>
       </c>
       <c r="J10" s="96">
-        <f t="shared" si="2"/>
-        <v>20640.604608000001</v>
+        <f t="shared" si="3"/>
+        <v>20640.565920000005</v>
       </c>
       <c r="K10" s="142">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>29871.661248000004</v>
       </c>
       <c r="L10" s="103">
-        <f t="shared" si="4"/>
-        <v>59466.18976478609</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="193">
+        <f t="shared" si="5"/>
+        <v>50512.227168000012</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="189">
         <v>7</v>
       </c>
-      <c r="B11" s="194"/>
+      <c r="B11" s="190"/>
       <c r="C11" s="110" t="s">
         <v>70</v>
       </c>
       <c r="D11" s="72"/>
       <c r="E11" s="149">
-        <v>54686.953726963213</v>
-      </c>
-      <c r="F11" s="150"/>
+        <v>87074.54727204176</v>
+      </c>
+      <c r="F11" s="150">
+        <f t="shared" si="0"/>
+        <v>87074.54727204176</v>
+      </c>
       <c r="G11" s="151">
-        <f t="shared" si="0"/>
-        <v>54686.953726963213</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H11" s="151">
-        <f t="shared" si="1"/>
-        <v>2187.4781490785285</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I11" s="95">
         <v>18.260000000000002</v>
       </c>
       <c r="J11" s="96">
-        <f t="shared" si="2"/>
-        <v>30200.115396000008</v>
+        <f t="shared" si="3"/>
+        <v>30200.058790000006</v>
       </c>
       <c r="K11" s="142">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>43706.453076000005</v>
       </c>
       <c r="L11" s="103">
-        <f t="shared" si="4"/>
-        <v>87074.54727204176</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="193" t="s">
+        <f t="shared" si="5"/>
+        <v>73906.511866000015</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="189" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="194"/>
+      <c r="B12" s="190"/>
       <c r="C12" s="110" t="str">
         <f>C9</f>
         <v>Grand Jorge</v>
       </c>
       <c r="D12" s="72"/>
       <c r="E12" s="149">
-        <v>3895.6564420000004</v>
-      </c>
-      <c r="F12" s="150"/>
+        <v>6267.7014636800004</v>
+      </c>
+      <c r="F12" s="150">
+        <f t="shared" si="0"/>
+        <v>6267.7014636800004</v>
+      </c>
       <c r="G12" s="151">
-        <f t="shared" si="0"/>
-        <v>3895.6564420000004</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H12" s="151">
-        <f t="shared" si="1"/>
-        <v>155.82625768000003</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I12" s="95">
         <v>1.34</v>
       </c>
       <c r="J12" s="96">
-        <f t="shared" si="2"/>
-        <v>2216.2187640000002</v>
+        <f t="shared" si="3"/>
+        <v>2216.2146100000004</v>
       </c>
       <c r="K12" s="142">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>3207.3738840000005</v>
       </c>
       <c r="L12" s="103">
-        <f t="shared" si="4"/>
-        <v>6267.7014636800004</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="193" t="s">
+        <f t="shared" si="5"/>
+        <v>5423.5884940000014</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="189" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="194"/>
+      <c r="B13" s="190"/>
       <c r="C13" s="110" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
       </c>
       <c r="D13" s="72"/>
       <c r="E13" s="149">
-        <v>3837.5123159999998</v>
-      </c>
-      <c r="F13" s="150"/>
+        <v>6174.1536806399999</v>
+      </c>
+      <c r="F13" s="150">
+        <f t="shared" si="0"/>
+        <v>6174.1536806399999</v>
+      </c>
       <c r="G13" s="151">
-        <f t="shared" si="0"/>
-        <v>3837.5123159999998</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H13" s="151">
-        <f t="shared" si="1"/>
-        <v>153.50049264</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I13" s="95">
         <v>1.32</v>
       </c>
       <c r="J13" s="96">
-        <f t="shared" si="2"/>
-        <v>2183.1408720000004</v>
+        <f t="shared" si="3"/>
+        <v>2183.1367800000003</v>
       </c>
       <c r="K13" s="142">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>3159.5026320000006</v>
       </c>
       <c r="L13" s="103">
-        <f t="shared" si="4"/>
-        <v>6174.1536806399999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="193" t="s">
+        <f t="shared" si="5"/>
+        <v>5342.6394120000004</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="189" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="194"/>
+      <c r="B14" s="190"/>
       <c r="C14" s="58" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
       </c>
       <c r="D14" s="72"/>
       <c r="E14" s="149">
-        <v>3837.5123159999998</v>
-      </c>
-      <c r="F14" s="150"/>
+        <v>6174.1536806399999</v>
+      </c>
+      <c r="F14" s="150">
+        <f t="shared" si="0"/>
+        <v>6174.1536806399999</v>
+      </c>
       <c r="G14" s="151">
-        <f t="shared" si="0"/>
-        <v>3837.5123159999998</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H14" s="151">
-        <f t="shared" si="1"/>
-        <v>153.50049264</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I14" s="95">
         <v>1.32</v>
       </c>
       <c r="J14" s="96">
-        <f t="shared" si="2"/>
-        <v>2183.1408720000004</v>
+        <f t="shared" si="3"/>
+        <v>2183.1367800000003</v>
       </c>
       <c r="K14" s="142">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>3159.5026320000006</v>
       </c>
       <c r="L14" s="103">
-        <f t="shared" si="4"/>
-        <v>6174.1536806399999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>5342.6394120000004</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="104" t="s">
         <v>11</v>
       </c>
@@ -3051,35 +3083,35 @@
       <c r="D15" s="106"/>
       <c r="E15" s="42">
         <f>SUM(E5:E14)</f>
-        <v>301017.59000000003</v>
+        <v>478447.75360000005</v>
       </c>
       <c r="F15" s="107">
         <f>SUM(F5:F14)</f>
-        <v>0</v>
+        <v>478447.75360000005</v>
       </c>
       <c r="G15" s="107"/>
       <c r="H15" s="108">
         <f>SUM(H5:H14)</f>
-        <v>12040.703600000001</v>
+        <v>0</v>
       </c>
       <c r="I15" s="109">
-        <f t="shared" ref="I15" si="5">SUM(I5:I14)</f>
+        <f t="shared" ref="I15" si="6">SUM(I5:I14)</f>
         <v>100</v>
       </c>
       <c r="J15" s="39">
         <f>SUM(J5:J14)</f>
-        <v>165389.46</v>
+        <v>165389.15000000002</v>
       </c>
       <c r="K15" s="42">
         <f>SUM(K5:K11)</f>
-        <v>0</v>
+        <v>229829.880852</v>
       </c>
       <c r="L15" s="42">
         <f>SUM(L5:L14)</f>
-        <v>478447.75360000005</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>404745.41000000015</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="52" t="s">
         <v>49</v>
       </c>
@@ -3087,7 +3119,7 @@
         <v>7454</v>
       </c>
     </row>
-    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="27" t="s">
         <v>51</v>
       </c>
@@ -3105,7 +3137,7 @@
       <c r="K19" s="53"/>
       <c r="L19" s="31"/>
     </row>
-    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>0</v>
       </c>
@@ -3137,7 +3169,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -3163,7 +3195,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
         <v>1</v>
       </c>
@@ -3197,7 +3229,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
         <v>2</v>
       </c>
@@ -3222,7 +3254,7 @@
         <v>0.122</v>
       </c>
       <c r="J23" s="44">
-        <f t="shared" ref="J23:J29" si="6">0*I23</f>
+        <f t="shared" ref="J23:J29" si="7">0*I23</f>
         <v>0</v>
       </c>
       <c r="K23" s="41"/>
@@ -3231,7 +3263,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
         <v>3</v>
       </c>
@@ -3257,7 +3289,7 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="J24" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K24" s="41"/>
@@ -3266,7 +3298,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11">
         <v>4</v>
       </c>
@@ -3288,7 +3320,7 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="J25" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K25" s="41"/>
@@ -3297,7 +3329,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11">
         <v>5</v>
       </c>
@@ -3319,7 +3351,7 @@
         <v>0.13700000000000001</v>
       </c>
       <c r="J26" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K26" s="41"/>
@@ -3328,7 +3360,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11">
         <v>6</v>
       </c>
@@ -3350,7 +3382,7 @@
         <v>0.13200000000000001</v>
       </c>
       <c r="J27" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K27" s="41"/>
@@ -3359,7 +3391,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11">
         <v>7</v>
       </c>
@@ -3384,7 +3416,7 @@
         <v>0.127</v>
       </c>
       <c r="J28" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K28" s="41"/>
@@ -3393,7 +3425,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11">
         <v>8</v>
       </c>
@@ -3418,7 +3450,7 @@
         <v>0.127</v>
       </c>
       <c r="J29" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K29" s="41"/>
@@ -3427,7 +3459,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
         <v>11</v>
       </c>
@@ -3447,11 +3479,11 @@
         <v>0</v>
       </c>
       <c r="I30" s="15">
-        <f t="shared" ref="I30:J30" si="7">SUM(I22:I29)</f>
+        <f t="shared" ref="I30:J30" si="8">SUM(I22:I29)</f>
         <v>1</v>
       </c>
       <c r="J30" s="39">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K30" s="42"/>
@@ -3460,12 +3492,12 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="180" t="s">
@@ -3481,7 +3513,7 @@
       <c r="M32" s="153"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="182" t="s">
@@ -3497,7 +3529,7 @@
       <c r="M33" s="155"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="152"/>
@@ -3514,7 +3546,7 @@
       <c r="M34" s="155"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="154" t="s">
@@ -3530,7 +3562,7 @@
       <c r="M35" s="155"/>
       <c r="N35"/>
     </row>
-    <row r="36" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="158"/>
@@ -3544,7 +3576,7 @@
       <c r="M36" s="155"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="183" t="s">
@@ -3560,7 +3592,7 @@
       <c r="M37" s="155"/>
       <c r="N37"/>
     </row>
-    <row r="38" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="154"/>
@@ -3574,7 +3606,7 @@
       <c r="M38" s="155"/>
       <c r="N38"/>
     </row>
-    <row r="39" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="154" t="s">
@@ -3599,7 +3631,7 @@
       <c r="M39" s="187"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="154" t="s">
@@ -3617,7 +3649,7 @@
       <c r="M40" s="155"/>
       <c r="N40"/>
     </row>
-    <row r="41" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="154"/>
@@ -3631,7 +3663,7 @@
       <c r="M41" s="187"/>
       <c r="N41"/>
     </row>
-    <row r="42" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="154" t="s">
@@ -3643,14 +3675,14 @@
       <c r="I42" s="157"/>
       <c r="J42" s="163">
         <f>J7</f>
-        <v>20607.526716000004</v>
+        <v>20607.488090000003</v>
       </c>
       <c r="K42" s="155"/>
       <c r="L42" s="154"/>
       <c r="M42" s="155"/>
       <c r="N42"/>
     </row>
-    <row r="43" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="164" t="s">
@@ -3662,14 +3694,14 @@
       <c r="I43" s="157"/>
       <c r="J43" s="163">
         <f>K7</f>
-        <v>0</v>
+        <v>29823.789996000003</v>
       </c>
       <c r="K43" s="155"/>
       <c r="L43" s="154"/>
       <c r="M43" s="155"/>
       <c r="N43"/>
     </row>
-    <row r="44" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="164" t="s">
@@ -3681,14 +3713,14 @@
       <c r="I44" s="157"/>
       <c r="J44" s="163">
         <f>G7+H7</f>
-        <v>39409.794500528704</v>
+        <v>0</v>
       </c>
       <c r="K44" s="155"/>
       <c r="L44" s="154"/>
       <c r="M44" s="155"/>
       <c r="N44"/>
     </row>
-    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="164"/>
@@ -3702,7 +3734,7 @@
       <c r="M45" s="155"/>
       <c r="N45"/>
     </row>
-    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="164"/>
@@ -3716,7 +3748,7 @@
       <c r="M46" s="155"/>
       <c r="N46"/>
     </row>
-    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="F47" s="157"/>
@@ -3729,7 +3761,7 @@
       <c r="M47" s="155"/>
       <c r="N47"/>
     </row>
-    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="164"/>
@@ -3743,7 +3775,7 @@
       <c r="M48" s="155"/>
       <c r="N48"/>
     </row>
-    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="154"/>
@@ -3757,7 +3789,7 @@
       <c r="M49" s="155"/>
       <c r="N49"/>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="154" t="s">
@@ -3776,7 +3808,7 @@
       <c r="M50" s="155"/>
       <c r="N50"/>
     </row>
-    <row r="51" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="154"/>
@@ -3790,7 +3822,7 @@
       <c r="M51" s="166"/>
       <c r="N51"/>
     </row>
-    <row r="52" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="176" t="s">
@@ -3802,20 +3834,20 @@
       <c r="I52" s="177"/>
       <c r="J52" s="178">
         <f>SUM(J42:J51)</f>
-        <v>60093.121216528714</v>
+        <v>50507.078086000009</v>
       </c>
       <c r="K52" s="179"/>
       <c r="L52" s="167"/>
       <c r="M52" s="168"/>
       <c r="N52"/>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="N53"/>
     </row>
-    <row r="55" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="56" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="56" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E56" s="180" t="s">
         <v>111</v>
       </c>
@@ -3828,7 +3860,7 @@
       <c r="L56" s="152"/>
       <c r="M56" s="153"/>
     </row>
-    <row r="57" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E57" s="182" t="s">
         <v>112</v>
       </c>
@@ -3841,7 +3873,7 @@
       <c r="L57" s="154"/>
       <c r="M57" s="155"/>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E58" s="152"/>
       <c r="F58" s="156"/>
       <c r="G58" s="156"/>
@@ -3855,7 +3887,7 @@
       <c r="L58" s="154"/>
       <c r="M58" s="155"/>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E59" s="154" t="s">
         <v>113</v>
       </c>
@@ -3868,7 +3900,7 @@
       <c r="L59" s="154"/>
       <c r="M59" s="155"/>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E60" s="158"/>
       <c r="F60" s="159"/>
       <c r="G60" s="159"/>
@@ -3879,7 +3911,7 @@
       <c r="L60" s="154"/>
       <c r="M60" s="155"/>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E61" s="183" t="s">
         <v>49</v>
       </c>
@@ -3892,7 +3924,7 @@
       <c r="L61" s="154"/>
       <c r="M61" s="155"/>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E62" s="154"/>
       <c r="F62" s="157"/>
       <c r="G62" s="157"/>
@@ -3903,7 +3935,7 @@
       <c r="L62" s="154"/>
       <c r="M62" s="155"/>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E63" s="154" t="s">
         <v>114</v>
       </c>
@@ -3925,7 +3957,7 @@
       </c>
       <c r="M63" s="187"/>
     </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E64" s="154" t="s">
         <v>117</v>
       </c>
@@ -3940,7 +3972,7 @@
       <c r="L64" s="154"/>
       <c r="M64" s="155"/>
     </row>
-    <row r="65" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E65" s="154"/>
       <c r="F65" s="157"/>
       <c r="G65" s="157"/>
@@ -3951,7 +3983,7 @@
       <c r="L65" s="188"/>
       <c r="M65" s="187"/>
     </row>
-    <row r="66" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E66" s="154" t="s">
         <v>48</v>
       </c>
@@ -3961,13 +3993,13 @@
       <c r="I66" s="157"/>
       <c r="J66" s="163">
         <f>J8</f>
-        <v>24394.945350000002</v>
+        <v>24394.899625000005</v>
       </c>
       <c r="K66" s="155"/>
       <c r="L66" s="154"/>
       <c r="M66" s="155"/>
     </row>
-    <row r="67" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E67" s="164" t="s">
         <v>118</v>
       </c>
@@ -3977,13 +4009,13 @@
       <c r="I67" s="157"/>
       <c r="J67" s="163">
         <f>K8</f>
-        <v>0</v>
+        <v>35305.048349999997</v>
       </c>
       <c r="K67" s="155"/>
       <c r="L67" s="154"/>
       <c r="M67" s="155"/>
     </row>
-    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E68" s="164" t="s">
         <v>120</v>
       </c>
@@ -3999,7 +4031,7 @@
       <c r="L68" s="154"/>
       <c r="M68" s="155"/>
     </row>
-    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E69" s="164"/>
       <c r="F69" s="157"/>
       <c r="G69" s="157"/>
@@ -4010,7 +4042,7 @@
       <c r="L69" s="154"/>
       <c r="M69" s="155"/>
     </row>
-    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E70" s="164"/>
       <c r="F70" s="157"/>
       <c r="G70" s="157"/>
@@ -4021,7 +4053,7 @@
       <c r="L70" s="154"/>
       <c r="M70" s="155"/>
     </row>
-    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="F71" s="157"/>
       <c r="G71" s="157"/>
       <c r="H71" s="157"/>
@@ -4031,7 +4063,7 @@
       <c r="L71" s="154"/>
       <c r="M71" s="155"/>
     </row>
-    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E72" s="164"/>
       <c r="F72" s="157"/>
       <c r="G72" s="157"/>
@@ -4042,7 +4074,7 @@
       <c r="L72" s="154"/>
       <c r="M72" s="155"/>
     </row>
-    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E73" s="154"/>
       <c r="F73" s="157"/>
       <c r="G73" s="157"/>
@@ -4053,7 +4085,7 @@
       <c r="L73" s="154"/>
       <c r="M73" s="155"/>
     </row>
-    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E74" s="154"/>
       <c r="F74" s="157"/>
       <c r="G74" s="157"/>
@@ -4064,7 +4096,7 @@
       <c r="L74" s="154"/>
       <c r="M74" s="155"/>
     </row>
-    <row r="75" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E75" s="154"/>
       <c r="F75" s="157"/>
       <c r="G75" s="157"/>
@@ -4075,7 +4107,7 @@
       <c r="L75" s="165"/>
       <c r="M75" s="166"/>
     </row>
-    <row r="76" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E76" s="176" t="s">
         <v>119</v>
       </c>
@@ -4085,14 +4117,14 @@
       <c r="I76" s="177"/>
       <c r="J76" s="178">
         <f>SUM(J66:J75)</f>
-        <v>24394.945350000002</v>
+        <v>59699.947975000003</v>
       </c>
       <c r="K76" s="179"/>
       <c r="L76" s="167"/>
       <c r="M76" s="168"/>
     </row>
-    <row r="82" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="83" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="83" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E83" s="180" t="s">
         <v>111</v>
       </c>
@@ -4105,7 +4137,7 @@
       <c r="L83" s="152"/>
       <c r="M83" s="153"/>
     </row>
-    <row r="84" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E84" s="182" t="s">
         <v>112</v>
       </c>
@@ -4118,7 +4150,7 @@
       <c r="L84" s="154"/>
       <c r="M84" s="155"/>
     </row>
-    <row r="85" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E85" s="152"/>
       <c r="F85" s="156"/>
       <c r="G85" s="156"/>
@@ -4132,7 +4164,7 @@
       <c r="L85" s="154"/>
       <c r="M85" s="155"/>
     </row>
-    <row r="86" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E86" s="154" t="s">
         <v>113</v>
       </c>
@@ -4145,7 +4177,7 @@
       <c r="L86" s="154"/>
       <c r="M86" s="155"/>
     </row>
-    <row r="87" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E87" s="158"/>
       <c r="F87" s="159"/>
       <c r="G87" s="159"/>
@@ -4156,7 +4188,7 @@
       <c r="L87" s="154"/>
       <c r="M87" s="155"/>
     </row>
-    <row r="88" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E88" s="183" t="s">
         <v>49</v>
       </c>
@@ -4169,7 +4201,7 @@
       <c r="L88" s="154"/>
       <c r="M88" s="155"/>
     </row>
-    <row r="89" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E89" s="154"/>
       <c r="F89" s="157"/>
       <c r="G89" s="157"/>
@@ -4180,7 +4212,7 @@
       <c r="L89" s="154"/>
       <c r="M89" s="155"/>
     </row>
-    <row r="90" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E90" s="154" t="s">
         <v>114</v>
       </c>
@@ -4202,7 +4234,7 @@
       </c>
       <c r="M90" s="187"/>
     </row>
-    <row r="91" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E91" s="154" t="s">
         <v>117</v>
       </c>
@@ -4217,7 +4249,7 @@
       <c r="L91" s="154"/>
       <c r="M91" s="155"/>
     </row>
-    <row r="92" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E92" s="154"/>
       <c r="F92" s="157"/>
       <c r="G92" s="157"/>
@@ -4228,7 +4260,7 @@
       <c r="L92" s="188"/>
       <c r="M92" s="187"/>
     </row>
-    <row r="93" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E93" s="154" t="s">
         <v>48</v>
       </c>
@@ -4238,13 +4270,13 @@
       <c r="I93" s="157"/>
       <c r="J93" s="163">
         <f>J10</f>
-        <v>20640.604608000001</v>
+        <v>20640.565920000005</v>
       </c>
       <c r="K93" s="155"/>
       <c r="L93" s="154"/>
       <c r="M93" s="155"/>
     </row>
-    <row r="94" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E94" s="164" t="s">
         <v>118</v>
       </c>
@@ -4254,13 +4286,13 @@
       <c r="I94" s="157"/>
       <c r="J94" s="163">
         <f>K10</f>
-        <v>0</v>
+        <v>29871.661248000004</v>
       </c>
       <c r="K94" s="155"/>
       <c r="L94" s="154"/>
       <c r="M94" s="155"/>
     </row>
-    <row r="95" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E95" s="164" t="s">
         <v>121</v>
       </c>
@@ -4275,7 +4307,7 @@
       <c r="L95" s="154"/>
       <c r="M95" s="155"/>
     </row>
-    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E96" s="164"/>
       <c r="F96" s="157"/>
       <c r="G96" s="157"/>
@@ -4286,7 +4318,7 @@
       <c r="L96" s="154"/>
       <c r="M96" s="155"/>
     </row>
-    <row r="97" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E97" s="164"/>
       <c r="F97" s="157"/>
       <c r="G97" s="157"/>
@@ -4297,7 +4329,7 @@
       <c r="L97" s="154"/>
       <c r="M97" s="155"/>
     </row>
-    <row r="98" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F98" s="157"/>
       <c r="G98" s="157"/>
       <c r="H98" s="157"/>
@@ -4307,7 +4339,7 @@
       <c r="L98" s="154"/>
       <c r="M98" s="155"/>
     </row>
-    <row r="99" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E99" s="164"/>
       <c r="F99" s="157"/>
       <c r="G99" s="157"/>
@@ -4318,7 +4350,7 @@
       <c r="L99" s="154"/>
       <c r="M99" s="155"/>
     </row>
-    <row r="100" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E100" s="154"/>
       <c r="F100" s="157"/>
       <c r="G100" s="157"/>
@@ -4329,7 +4361,7 @@
       <c r="L100" s="154"/>
       <c r="M100" s="155"/>
     </row>
-    <row r="101" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E101" s="154"/>
       <c r="F101" s="157"/>
       <c r="G101" s="157"/>
@@ -4340,7 +4372,7 @@
       <c r="L101" s="154"/>
       <c r="M101" s="155"/>
     </row>
-    <row r="102" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E102" s="154"/>
       <c r="F102" s="157"/>
       <c r="G102" s="157"/>
@@ -4351,7 +4383,7 @@
       <c r="L102" s="165"/>
       <c r="M102" s="166"/>
     </row>
-    <row r="103" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E103" s="176" t="s">
         <v>119</v>
       </c>
@@ -4361,14 +4393,14 @@
       <c r="I103" s="177"/>
       <c r="J103" s="178">
         <f>SUM(J93:J102)</f>
-        <v>20664.494608000001</v>
+        <v>50536.117168000012</v>
       </c>
       <c r="K103" s="179"/>
       <c r="L103" s="167"/>
       <c r="M103" s="168"/>
     </row>
-    <row r="107" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="108" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="108" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E108" s="180" t="s">
         <v>111</v>
       </c>
@@ -4381,7 +4413,7 @@
       <c r="L108" s="152"/>
       <c r="M108" s="153"/>
     </row>
-    <row r="109" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E109" s="182" t="s">
         <v>112</v>
       </c>
@@ -4394,7 +4426,7 @@
       <c r="L109" s="154"/>
       <c r="M109" s="155"/>
     </row>
-    <row r="110" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E110" s="152"/>
       <c r="F110" s="156"/>
       <c r="G110" s="156"/>
@@ -4408,7 +4440,7 @@
       <c r="L110" s="154"/>
       <c r="M110" s="155"/>
     </row>
-    <row r="111" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E111" s="154" t="s">
         <v>113</v>
       </c>
@@ -4421,7 +4453,7 @@
       <c r="L111" s="154"/>
       <c r="M111" s="155"/>
     </row>
-    <row r="112" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E112" s="158"/>
       <c r="F112" s="159"/>
       <c r="G112" s="159"/>
@@ -4432,7 +4464,7 @@
       <c r="L112" s="154"/>
       <c r="M112" s="155"/>
     </row>
-    <row r="113" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E113" s="183" t="s">
         <v>49</v>
       </c>
@@ -4445,7 +4477,7 @@
       <c r="L113" s="154"/>
       <c r="M113" s="155"/>
     </row>
-    <row r="114" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E114" s="154"/>
       <c r="F114" s="157"/>
       <c r="G114" s="157"/>
@@ -4456,7 +4488,7 @@
       <c r="L114" s="154"/>
       <c r="M114" s="155"/>
     </row>
-    <row r="115" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E115" s="154" t="s">
         <v>114</v>
       </c>
@@ -4478,7 +4510,7 @@
       </c>
       <c r="M115" s="187"/>
     </row>
-    <row r="116" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E116" s="154" t="s">
         <v>117</v>
       </c>
@@ -4493,7 +4525,7 @@
       <c r="L116" s="154"/>
       <c r="M116" s="155"/>
     </row>
-    <row r="117" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E117" s="154"/>
       <c r="F117" s="157"/>
       <c r="G117" s="157"/>
@@ -4504,7 +4536,7 @@
       <c r="L117" s="188"/>
       <c r="M117" s="187"/>
     </row>
-    <row r="118" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E118" s="154" t="s">
         <v>48</v>
       </c>
@@ -4514,13 +4546,13 @@
       <c r="I118" s="157"/>
       <c r="J118" s="163">
         <f>J5</f>
-        <v>22823.745480000005</v>
+        <v>22823.702700000005</v>
       </c>
       <c r="K118" s="155"/>
       <c r="L118" s="154"/>
       <c r="M118" s="155"/>
     </row>
-    <row r="119" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E119" s="164" t="s">
         <v>118</v>
       </c>
@@ -4530,13 +4562,13 @@
       <c r="I119" s="157"/>
       <c r="J119" s="163">
         <f>K5</f>
-        <v>0</v>
+        <v>33031.16388</v>
       </c>
       <c r="K119" s="155"/>
       <c r="L119" s="154"/>
       <c r="M119" s="155"/>
     </row>
-    <row r="120" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E120" s="164" t="s">
         <v>122</v>
       </c>
@@ -4552,7 +4584,7 @@
       <c r="L120" s="154"/>
       <c r="M120" s="155"/>
     </row>
-    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E121" s="164"/>
       <c r="F121" s="157"/>
       <c r="G121" s="157"/>
@@ -4563,7 +4595,7 @@
       <c r="L121" s="154"/>
       <c r="M121" s="155"/>
     </row>
-    <row r="122" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E122" s="164"/>
       <c r="F122" s="157"/>
       <c r="G122" s="157"/>
@@ -4574,7 +4606,7 @@
       <c r="L122" s="154"/>
       <c r="M122" s="155"/>
     </row>
-    <row r="123" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F123" s="157"/>
       <c r="G123" s="157"/>
       <c r="H123" s="157"/>
@@ -4584,7 +4616,7 @@
       <c r="L123" s="154"/>
       <c r="M123" s="155"/>
     </row>
-    <row r="124" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E124" s="164"/>
       <c r="F124" s="157"/>
       <c r="G124" s="157"/>
@@ -4595,7 +4627,7 @@
       <c r="L124" s="154"/>
       <c r="M124" s="155"/>
     </row>
-    <row r="125" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E125" s="154"/>
       <c r="F125" s="157"/>
       <c r="G125" s="157"/>
@@ -4606,7 +4638,7 @@
       <c r="L125" s="154"/>
       <c r="M125" s="155"/>
     </row>
-    <row r="126" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E126" s="154"/>
       <c r="F126" s="157"/>
       <c r="G126" s="157"/>
@@ -4617,7 +4649,7 @@
       <c r="L126" s="154"/>
       <c r="M126" s="155"/>
     </row>
-    <row r="127" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E127" s="154"/>
       <c r="F127" s="157"/>
       <c r="G127" s="157"/>
@@ -4628,7 +4660,7 @@
       <c r="L127" s="165"/>
       <c r="M127" s="166"/>
     </row>
-    <row r="128" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E128" s="176" t="s">
         <v>119</v>
       </c>
@@ -4638,7 +4670,7 @@
       <c r="I128" s="177"/>
       <c r="J128" s="178">
         <f>SUM(J118:J127)</f>
-        <v>22771.405480000005</v>
+        <v>55802.526580000005</v>
       </c>
       <c r="K128" s="179"/>
       <c r="L128" s="167"/>
@@ -4646,6 +4678,16 @@
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="L65:M65"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="A3:B4"/>
     <mergeCell ref="A5:B5"/>
@@ -4657,18 +4699,6 @@
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="L65:M65"/>
-    <mergeCell ref="E76:I76"/>
-    <mergeCell ref="J76:K76"/>
     <mergeCell ref="E83:K83"/>
     <mergeCell ref="L115:M115"/>
     <mergeCell ref="L117:M117"/>
@@ -4692,6 +4722,8 @@
     <mergeCell ref="E32:K32"/>
     <mergeCell ref="E33:K33"/>
     <mergeCell ref="E37:K37"/>
+    <mergeCell ref="E76:I76"/>
+    <mergeCell ref="J76:K76"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -4702,16 +4734,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="7" width="15.42578125" customWidth="1"/>
-    <col min="8" max="8" width="18.28515625" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" customWidth="1"/>
-    <col min="10" max="10" width="22.5703125" customWidth="1"/>
-    <col min="11" max="11" width="13.85546875" customWidth="1"/>
+    <col min="6" max="7" width="15.44140625" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" customWidth="1"/>
+    <col min="10" max="10" width="22.5546875" customWidth="1"/>
+    <col min="11" max="11" width="13.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B1" s="111" t="s">
         <v>79</v>
       </c>
@@ -4731,12 +4763,12 @@
       <c r="K1" s="114"/>
       <c r="L1" s="115"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="H2" s="116"/>
       <c r="I2" s="116"/>
       <c r="J2" s="116"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B3" s="117" t="s">
         <v>82</v>
       </c>
@@ -4763,7 +4795,7 @@
       <c r="K3" s="5"/>
       <c r="M3" s="119"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B4" s="117"/>
       <c r="C4" s="111" t="s">
         <v>88</v>
@@ -4780,7 +4812,7 @@
       <c r="I4" s="120"/>
       <c r="J4" s="120"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>90</v>
       </c>
@@ -4813,7 +4845,7 @@
       <c r="L5" s="122"/>
       <c r="M5" s="123"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>91</v>
       </c>
@@ -4846,7 +4878,7 @@
       <c r="L6" s="122"/>
       <c r="M6" s="123"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>92</v>
       </c>
@@ -4878,7 +4910,7 @@
       <c r="L7" s="122"/>
       <c r="M7" s="123"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>93</v>
       </c>
@@ -4911,7 +4943,7 @@
       <c r="L8" s="122"/>
       <c r="M8" s="123"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>94</v>
       </c>
@@ -4944,7 +4976,7 @@
       <c r="L9" s="122"/>
       <c r="M9" s="123"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>95</v>
       </c>
@@ -4977,7 +5009,7 @@
       <c r="L10" s="122"/>
       <c r="M10" s="123"/>
     </row>
-    <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>96</v>
       </c>
@@ -5010,7 +5042,7 @@
       <c r="L11" s="122"/>
       <c r="M11" s="123"/>
     </row>
-    <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="125"/>
       <c r="C12" s="126">
         <f>SUM(C5:C11)</f>
@@ -5038,13 +5070,13 @@
       <c r="K12" s="125"/>
       <c r="L12" s="128"/>
     </row>
-    <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C13" s="129"/>
       <c r="H13" s="117"/>
       <c r="I13" s="117"/>
       <c r="J13" s="117"/>
     </row>
-    <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>97</v>
       </c>
@@ -5056,7 +5088,7 @@
       <c r="I14" s="117"/>
       <c r="J14" s="117"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>98</v>
       </c>
@@ -5064,7 +5096,7 @@
       <c r="I15" s="117"/>
       <c r="J15" s="117"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B16" s="117"/>
       <c r="C16" s="111"/>
       <c r="D16" s="111"/>
@@ -5075,7 +5107,7 @@
       <c r="J16" s="111"/>
       <c r="K16" s="5"/>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B17" s="117"/>
       <c r="C17" s="111"/>
       <c r="D17" s="111"/>
@@ -5085,12 +5117,12 @@
       <c r="I17" s="120"/>
       <c r="J17" s="120"/>
     </row>
-    <row r="18" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H18" s="117"/>
       <c r="I18" s="117"/>
       <c r="J18" s="117"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C19" s="131"/>
       <c r="D19" s="132"/>
       <c r="E19" s="132"/>
@@ -5103,7 +5135,7 @@
       <c r="L19" s="132"/>
       <c r="M19" s="134"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C20" s="135"/>
       <c r="E20" t="s">
         <v>99</v>
@@ -5119,7 +5151,7 @@
       </c>
       <c r="M20" s="137"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C21" s="135"/>
       <c r="D21" t="s">
         <v>101</v>
@@ -5141,7 +5173,7 @@
       </c>
       <c r="M21" s="137"/>
     </row>
-    <row r="22" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C22" s="138"/>
       <c r="D22" s="139"/>
       <c r="E22" s="139"/>
@@ -5154,16 +5186,16 @@
       <c r="L22" s="139"/>
       <c r="M22" s="140"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K25" s="141" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="G26" s="5"/>
       <c r="K26" s="119"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="I27" t="s">
         <v>105</v>
       </c>
@@ -5174,7 +5206,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="G28" s="5"/>
       <c r="H28" s="5" t="s">
         <v>95</v>
@@ -5190,7 +5222,7 @@
         <v>45829</v>
       </c>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
       <c r="J31" t="s">
         <v>107</v>
       </c>
@@ -5198,7 +5230,7 @@
         <v>117067</v>
       </c>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
       <c r="J32" t="s">
         <v>108</v>
       </c>
@@ -5206,7 +5238,7 @@
         <v>-55000</v>
       </c>
     </row>
-    <row r="33" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J33" s="119" t="s">
         <v>109</v>
       </c>
@@ -5214,7 +5246,7 @@
         <v>43965</v>
       </c>
     </row>
-    <row r="34" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K34" s="113">
         <f>SUM(K31:K33)</f>
         <v>106032</v>
@@ -5229,22 +5261,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="12" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" customWidth="1"/>
-    <col min="9" max="9" width="0.140625" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="11.109375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
+    <col min="9" max="9" width="0.109375" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="0.140625" customWidth="1"/>
+    <col min="11" max="11" width="0.109375" customWidth="1"/>
     <col min="12" max="13" width="12" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D1" s="55">
         <v>50000</v>
       </c>
@@ -5254,14 +5286,14 @@
       <c r="I1" s="207"/>
       <c r="J1" s="207"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="52" t="s">
         <v>49</v>
       </c>
       <c r="B2" s="1"/>
       <c r="P2" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>56</v>
       </c>
@@ -5284,7 +5316,7 @@
       <c r="N3" s="31"/>
       <c r="P3" s="21"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -5327,7 +5359,7 @@
       </c>
       <c r="P4" s="21"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -5358,7 +5390,7 @@
       <c r="N5" s="204"/>
       <c r="P5" s="21"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>1</v>
       </c>
@@ -5406,7 +5438,7 @@
       </c>
       <c r="P6" s="21"/>
     </row>
-    <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>2</v>
       </c>
@@ -5454,7 +5486,7 @@
       </c>
       <c r="P7" s="21"/>
     </row>
-    <row r="8" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>3</v>
       </c>
@@ -5502,7 +5534,7 @@
       </c>
       <c r="P8" s="21"/>
     </row>
-    <row r="9" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="27" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>4</v>
       </c>
@@ -5550,7 +5582,7 @@
       </c>
       <c r="P9" s="21"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>5</v>
       </c>
@@ -5598,7 +5630,7 @@
       </c>
       <c r="P10" s="21"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
         <v>6</v>
       </c>
@@ -5646,7 +5678,7 @@
       </c>
       <c r="P11" s="21"/>
     </row>
-    <row r="12" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <v>7</v>
       </c>
@@ -5694,7 +5726,7 @@
       </c>
       <c r="P12" s="21"/>
     </row>
-    <row r="13" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="27" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
         <v>8</v>
       </c>
@@ -5742,7 +5774,7 @@
       </c>
       <c r="P13" s="21"/>
     </row>
-    <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>11</v>
       </c>
@@ -5808,24 +5840,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N128"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="1.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" customWidth="1"/>
-    <col min="9" max="9" width="8.28515625" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.5703125" style="21"/>
+    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="1.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.44140625" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5546875" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="209" t="s">
         <v>126</v>
       </c>
@@ -5843,7 +5875,7 @@
       </c>
       <c r="J1" s="210"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="97"/>
       <c r="B2" s="98"/>
       <c r="C2" s="99"/>
@@ -5857,15 +5889,15 @@
       <c r="K2" s="101"/>
       <c r="L2" s="102"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="199" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="195" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="200"/>
-      <c r="C3" s="189" t="s">
+      <c r="B3" s="196"/>
+      <c r="C3" s="191" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="197" t="s">
+      <c r="D3" s="193" t="s">
         <v>55</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -5874,16 +5906,16 @@
       <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="189" t="s">
+      <c r="G3" s="191" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="189" t="s">
+      <c r="H3" s="191" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="195" t="s">
+      <c r="I3" s="201" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="197" t="s">
+      <c r="J3" s="193" t="s">
         <v>128</v>
       </c>
       <c r="K3" s="170" t="s">
@@ -5893,31 +5925,31 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="201"/>
-      <c r="B4" s="202"/>
-      <c r="C4" s="190"/>
-      <c r="D4" s="198"/>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="197"/>
+      <c r="B4" s="198"/>
+      <c r="C4" s="192"/>
+      <c r="D4" s="194"/>
       <c r="E4" s="57" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="196"/>
-      <c r="J4" s="198"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="202"/>
+      <c r="J4" s="194"/>
       <c r="K4" s="171" t="s">
         <v>129</v>
       </c>
       <c r="L4" s="212"/>
     </row>
-    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="193">
+    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="189">
         <v>1</v>
       </c>
-      <c r="B5" s="194"/>
+      <c r="B5" s="190"/>
       <c r="C5" s="110" t="s">
         <v>65</v>
       </c>
@@ -5953,11 +5985,11 @@
         <v>110400</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="193">
+    <row r="6" spans="1:12" ht="27" x14ac:dyDescent="0.3">
+      <c r="A6" s="189">
         <v>2</v>
       </c>
-      <c r="B6" s="194"/>
+      <c r="B6" s="190"/>
       <c r="C6" s="110" t="s">
         <v>66</v>
       </c>
@@ -5995,11 +6027,11 @@
         <v>64880.003495999961</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="193">
+    <row r="7" spans="1:12" ht="27" x14ac:dyDescent="0.3">
+      <c r="A7" s="189">
         <v>3</v>
       </c>
-      <c r="B7" s="194"/>
+      <c r="B7" s="190"/>
       <c r="C7" s="110" t="s">
         <v>66</v>
       </c>
@@ -6037,11 +6069,11 @@
         <v>99680</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="193">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="189">
         <v>4</v>
       </c>
-      <c r="B8" s="194"/>
+      <c r="B8" s="190"/>
       <c r="C8" s="110" t="s">
         <v>67</v>
       </c>
@@ -6079,11 +6111,11 @@
         <v>118000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="193">
+    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="189">
         <v>5</v>
       </c>
-      <c r="B9" s="194"/>
+      <c r="B9" s="190"/>
       <c r="C9" s="110" t="s">
         <v>68</v>
       </c>
@@ -6121,11 +6153,11 @@
         <v>99279.992624999984</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="193">
+    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="189">
         <v>6</v>
       </c>
-      <c r="B10" s="194"/>
+      <c r="B10" s="190"/>
       <c r="C10" s="110" t="s">
         <v>69</v>
       </c>
@@ -6161,11 +6193,11 @@
         <v>94999.311648000003</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="193">
+    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="189">
         <v>7</v>
       </c>
-      <c r="B11" s="194"/>
+      <c r="B11" s="190"/>
       <c r="C11" s="110" t="s">
         <v>70</v>
       </c>
@@ -6201,11 +6233,11 @@
         <v>146080.00000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="193" t="s">
+    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="189" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="194"/>
+      <c r="B12" s="190"/>
       <c r="C12" s="110" t="str">
         <f>C9</f>
         <v>Grand Jorge</v>
@@ -6242,11 +6274,11 @@
         <v>10720</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="193" t="s">
+    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="189" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="194"/>
+      <c r="B13" s="190"/>
       <c r="C13" s="110" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -6283,11 +6315,11 @@
         <v>10560</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="193" t="s">
+    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="189" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="194"/>
+      <c r="B14" s="190"/>
       <c r="C14" s="58" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -6324,7 +6356,7 @@
         <v>10560</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="104" t="s">
         <v>11</v>
       </c>
@@ -6364,7 +6396,7 @@
         <v>765159.30776899995</v>
       </c>
     </row>
-    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="52" t="s">
         <v>49</v>
       </c>
@@ -6372,7 +6404,7 @@
         <v>7454</v>
       </c>
     </row>
-    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="27" t="s">
         <v>51</v>
       </c>
@@ -6390,7 +6422,7 @@
       <c r="K19" s="53"/>
       <c r="L19" s="31"/>
     </row>
-    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>0</v>
       </c>
@@ -6422,7 +6454,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -6448,7 +6480,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
         <v>1</v>
       </c>
@@ -6482,7 +6514,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
         <v>2</v>
       </c>
@@ -6516,7 +6548,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
         <v>3</v>
       </c>
@@ -6551,7 +6583,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11">
         <v>4</v>
       </c>
@@ -6582,7 +6614,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11">
         <v>5</v>
       </c>
@@ -6613,7 +6645,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11">
         <v>6</v>
       </c>
@@ -6644,7 +6676,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11">
         <v>7</v>
       </c>
@@ -6678,7 +6710,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11">
         <v>8</v>
       </c>
@@ -6712,7 +6744,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
         <v>11</v>
       </c>
@@ -6745,12 +6777,12 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="180" t="s">
@@ -6766,7 +6798,7 @@
       <c r="M32" s="153"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="182" t="s">
@@ -6782,7 +6814,7 @@
       <c r="M33" s="155"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="152"/>
@@ -6799,7 +6831,7 @@
       <c r="M34" s="155"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="154" t="s">
@@ -6815,7 +6847,7 @@
       <c r="M35" s="155"/>
       <c r="N35"/>
     </row>
-    <row r="36" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="158"/>
@@ -6829,7 +6861,7 @@
       <c r="M36" s="155"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="183" t="s">
@@ -6845,7 +6877,7 @@
       <c r="M37" s="155"/>
       <c r="N37"/>
     </row>
-    <row r="38" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="154"/>
@@ -6859,7 +6891,7 @@
       <c r="M38" s="155"/>
       <c r="N38"/>
     </row>
-    <row r="39" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="154" t="s">
@@ -6884,7 +6916,7 @@
       <c r="M39" s="187"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="154" t="s">
@@ -6902,7 +6934,7 @@
       <c r="M40" s="155"/>
       <c r="N40"/>
     </row>
-    <row r="41" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="154"/>
@@ -6916,7 +6948,7 @@
       <c r="M41" s="187"/>
       <c r="N41"/>
     </row>
-    <row r="42" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="154" t="s">
@@ -6935,7 +6967,7 @@
       <c r="M42" s="155"/>
       <c r="N42"/>
     </row>
-    <row r="43" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="164" t="s">
@@ -6954,7 +6986,7 @@
       <c r="M43" s="155"/>
       <c r="N43"/>
     </row>
-    <row r="44" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="164" t="s">
@@ -6973,7 +7005,7 @@
       <c r="M44" s="155"/>
       <c r="N44"/>
     </row>
-    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="164"/>
@@ -6987,7 +7019,7 @@
       <c r="M45" s="155"/>
       <c r="N45"/>
     </row>
-    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="164"/>
@@ -7001,7 +7033,7 @@
       <c r="M46" s="155"/>
       <c r="N46"/>
     </row>
-    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="F47" s="157"/>
@@ -7014,7 +7046,7 @@
       <c r="M47" s="155"/>
       <c r="N47"/>
     </row>
-    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="164"/>
@@ -7028,7 +7060,7 @@
       <c r="M48" s="155"/>
       <c r="N48"/>
     </row>
-    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="154"/>
@@ -7042,7 +7074,7 @@
       <c r="M49" s="155"/>
       <c r="N49"/>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="154" t="s">
@@ -7061,7 +7093,7 @@
       <c r="M50" s="155"/>
       <c r="N50"/>
     </row>
-    <row r="51" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="154"/>
@@ -7075,7 +7107,7 @@
       <c r="M51" s="166"/>
       <c r="N51"/>
     </row>
-    <row r="52" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="176" t="s">
@@ -7094,13 +7126,13 @@
       <c r="M52" s="168"/>
       <c r="N52"/>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="N53"/>
     </row>
-    <row r="55" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="56" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="56" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E56" s="180" t="s">
         <v>111</v>
       </c>
@@ -7113,7 +7145,7 @@
       <c r="L56" s="152"/>
       <c r="M56" s="153"/>
     </row>
-    <row r="57" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E57" s="182" t="s">
         <v>112</v>
       </c>
@@ -7126,7 +7158,7 @@
       <c r="L57" s="154"/>
       <c r="M57" s="155"/>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E58" s="152"/>
       <c r="F58" s="156"/>
       <c r="G58" s="156"/>
@@ -7140,7 +7172,7 @@
       <c r="L58" s="154"/>
       <c r="M58" s="155"/>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E59" s="154" t="s">
         <v>113</v>
       </c>
@@ -7153,7 +7185,7 @@
       <c r="L59" s="154"/>
       <c r="M59" s="155"/>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E60" s="158"/>
       <c r="F60" s="159"/>
       <c r="G60" s="159"/>
@@ -7164,7 +7196,7 @@
       <c r="L60" s="154"/>
       <c r="M60" s="155"/>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E61" s="183" t="s">
         <v>49</v>
       </c>
@@ -7177,7 +7209,7 @@
       <c r="L61" s="154"/>
       <c r="M61" s="155"/>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E62" s="154"/>
       <c r="F62" s="157"/>
       <c r="G62" s="157"/>
@@ -7188,7 +7220,7 @@
       <c r="L62" s="154"/>
       <c r="M62" s="155"/>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E63" s="154" t="s">
         <v>114</v>
       </c>
@@ -7210,7 +7242,7 @@
       </c>
       <c r="M63" s="187"/>
     </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E64" s="154" t="s">
         <v>117</v>
       </c>
@@ -7225,7 +7257,7 @@
       <c r="L64" s="154"/>
       <c r="M64" s="155"/>
     </row>
-    <row r="65" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E65" s="154"/>
       <c r="F65" s="157"/>
       <c r="G65" s="157"/>
@@ -7236,7 +7268,7 @@
       <c r="L65" s="188"/>
       <c r="M65" s="187"/>
     </row>
-    <row r="66" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E66" s="154" t="s">
         <v>48</v>
       </c>
@@ -7252,7 +7284,7 @@
       <c r="L66" s="154"/>
       <c r="M66" s="155"/>
     </row>
-    <row r="67" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E67" s="164" t="s">
         <v>118</v>
       </c>
@@ -7268,7 +7300,7 @@
       <c r="L67" s="154"/>
       <c r="M67" s="155"/>
     </row>
-    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E68" s="164" t="s">
         <v>120</v>
       </c>
@@ -7284,7 +7316,7 @@
       <c r="L68" s="154"/>
       <c r="M68" s="155"/>
     </row>
-    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E69" s="164"/>
       <c r="F69" s="157"/>
       <c r="G69" s="157"/>
@@ -7295,7 +7327,7 @@
       <c r="L69" s="154"/>
       <c r="M69" s="155"/>
     </row>
-    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E70" s="164"/>
       <c r="F70" s="157"/>
       <c r="G70" s="157"/>
@@ -7306,7 +7338,7 @@
       <c r="L70" s="154"/>
       <c r="M70" s="155"/>
     </row>
-    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="F71" s="157"/>
       <c r="G71" s="157"/>
       <c r="H71" s="157"/>
@@ -7316,7 +7348,7 @@
       <c r="L71" s="154"/>
       <c r="M71" s="155"/>
     </row>
-    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E72" s="164"/>
       <c r="F72" s="157"/>
       <c r="G72" s="157"/>
@@ -7327,7 +7359,7 @@
       <c r="L72" s="154"/>
       <c r="M72" s="155"/>
     </row>
-    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E73" s="154"/>
       <c r="F73" s="157"/>
       <c r="G73" s="157"/>
@@ -7338,7 +7370,7 @@
       <c r="L73" s="154"/>
       <c r="M73" s="155"/>
     </row>
-    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E74" s="154"/>
       <c r="F74" s="157"/>
       <c r="G74" s="157"/>
@@ -7349,7 +7381,7 @@
       <c r="L74" s="154"/>
       <c r="M74" s="155"/>
     </row>
-    <row r="75" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E75" s="154"/>
       <c r="F75" s="157"/>
       <c r="G75" s="157"/>
@@ -7360,7 +7392,7 @@
       <c r="L75" s="165"/>
       <c r="M75" s="166"/>
     </row>
-    <row r="76" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E76" s="176" t="s">
         <v>119</v>
       </c>
@@ -7376,8 +7408,8 @@
       <c r="L76" s="167"/>
       <c r="M76" s="168"/>
     </row>
-    <row r="82" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="83" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="83" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E83" s="180" t="s">
         <v>111</v>
       </c>
@@ -7390,7 +7422,7 @@
       <c r="L83" s="152"/>
       <c r="M83" s="153"/>
     </row>
-    <row r="84" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E84" s="182" t="s">
         <v>112</v>
       </c>
@@ -7403,7 +7435,7 @@
       <c r="L84" s="154"/>
       <c r="M84" s="155"/>
     </row>
-    <row r="85" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E85" s="152"/>
       <c r="F85" s="156"/>
       <c r="G85" s="156"/>
@@ -7417,7 +7449,7 @@
       <c r="L85" s="154"/>
       <c r="M85" s="155"/>
     </row>
-    <row r="86" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E86" s="154" t="s">
         <v>113</v>
       </c>
@@ -7430,7 +7462,7 @@
       <c r="L86" s="154"/>
       <c r="M86" s="155"/>
     </row>
-    <row r="87" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E87" s="158"/>
       <c r="F87" s="159"/>
       <c r="G87" s="159"/>
@@ -7441,7 +7473,7 @@
       <c r="L87" s="154"/>
       <c r="M87" s="155"/>
     </row>
-    <row r="88" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E88" s="183" t="s">
         <v>49</v>
       </c>
@@ -7454,7 +7486,7 @@
       <c r="L88" s="154"/>
       <c r="M88" s="155"/>
     </row>
-    <row r="89" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E89" s="154"/>
       <c r="F89" s="157"/>
       <c r="G89" s="157"/>
@@ -7465,7 +7497,7 @@
       <c r="L89" s="154"/>
       <c r="M89" s="155"/>
     </row>
-    <row r="90" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E90" s="154" t="s">
         <v>114</v>
       </c>
@@ -7487,7 +7519,7 @@
       </c>
       <c r="M90" s="187"/>
     </row>
-    <row r="91" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E91" s="154" t="s">
         <v>117</v>
       </c>
@@ -7502,7 +7534,7 @@
       <c r="L91" s="154"/>
       <c r="M91" s="155"/>
     </row>
-    <row r="92" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E92" s="154"/>
       <c r="F92" s="157"/>
       <c r="G92" s="157"/>
@@ -7513,7 +7545,7 @@
       <c r="L92" s="188"/>
       <c r="M92" s="187"/>
     </row>
-    <row r="93" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E93" s="154" t="s">
         <v>48</v>
       </c>
@@ -7529,7 +7561,7 @@
       <c r="L93" s="154"/>
       <c r="M93" s="155"/>
     </row>
-    <row r="94" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E94" s="164" t="s">
         <v>118</v>
       </c>
@@ -7545,7 +7577,7 @@
       <c r="L94" s="154"/>
       <c r="M94" s="155"/>
     </row>
-    <row r="95" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E95" s="164" t="s">
         <v>121</v>
       </c>
@@ -7560,7 +7592,7 @@
       <c r="L95" s="154"/>
       <c r="M95" s="155"/>
     </row>
-    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E96" s="164"/>
       <c r="F96" s="157"/>
       <c r="G96" s="157"/>
@@ -7571,7 +7603,7 @@
       <c r="L96" s="154"/>
       <c r="M96" s="155"/>
     </row>
-    <row r="97" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E97" s="164"/>
       <c r="F97" s="157"/>
       <c r="G97" s="157"/>
@@ -7582,7 +7614,7 @@
       <c r="L97" s="154"/>
       <c r="M97" s="155"/>
     </row>
-    <row r="98" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F98" s="157"/>
       <c r="G98" s="157"/>
       <c r="H98" s="157"/>
@@ -7592,7 +7624,7 @@
       <c r="L98" s="154"/>
       <c r="M98" s="155"/>
     </row>
-    <row r="99" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E99" s="164"/>
       <c r="F99" s="157"/>
       <c r="G99" s="157"/>
@@ -7603,7 +7635,7 @@
       <c r="L99" s="154"/>
       <c r="M99" s="155"/>
     </row>
-    <row r="100" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E100" s="154"/>
       <c r="F100" s="157"/>
       <c r="G100" s="157"/>
@@ -7614,7 +7646,7 @@
       <c r="L100" s="154"/>
       <c r="M100" s="155"/>
     </row>
-    <row r="101" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E101" s="154"/>
       <c r="F101" s="157"/>
       <c r="G101" s="157"/>
@@ -7625,7 +7657,7 @@
       <c r="L101" s="154"/>
       <c r="M101" s="155"/>
     </row>
-    <row r="102" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E102" s="154"/>
       <c r="F102" s="157"/>
       <c r="G102" s="157"/>
@@ -7636,7 +7668,7 @@
       <c r="L102" s="165"/>
       <c r="M102" s="166"/>
     </row>
-    <row r="103" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E103" s="176" t="s">
         <v>119</v>
       </c>
@@ -7652,8 +7684,8 @@
       <c r="L103" s="167"/>
       <c r="M103" s="168"/>
     </row>
-    <row r="107" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="108" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="108" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E108" s="180" t="s">
         <v>111</v>
       </c>
@@ -7666,7 +7698,7 @@
       <c r="L108" s="152"/>
       <c r="M108" s="153"/>
     </row>
-    <row r="109" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E109" s="182" t="s">
         <v>112</v>
       </c>
@@ -7679,7 +7711,7 @@
       <c r="L109" s="154"/>
       <c r="M109" s="155"/>
     </row>
-    <row r="110" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E110" s="152"/>
       <c r="F110" s="156"/>
       <c r="G110" s="156"/>
@@ -7693,7 +7725,7 @@
       <c r="L110" s="154"/>
       <c r="M110" s="155"/>
     </row>
-    <row r="111" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E111" s="154" t="s">
         <v>113</v>
       </c>
@@ -7706,7 +7738,7 @@
       <c r="L111" s="154"/>
       <c r="M111" s="155"/>
     </row>
-    <row r="112" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E112" s="158"/>
       <c r="F112" s="159"/>
       <c r="G112" s="159"/>
@@ -7717,7 +7749,7 @@
       <c r="L112" s="154"/>
       <c r="M112" s="155"/>
     </row>
-    <row r="113" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E113" s="183" t="s">
         <v>49</v>
       </c>
@@ -7730,7 +7762,7 @@
       <c r="L113" s="154"/>
       <c r="M113" s="155"/>
     </row>
-    <row r="114" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E114" s="154"/>
       <c r="F114" s="157"/>
       <c r="G114" s="157"/>
@@ -7741,7 +7773,7 @@
       <c r="L114" s="154"/>
       <c r="M114" s="155"/>
     </row>
-    <row r="115" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E115" s="154" t="s">
         <v>114</v>
       </c>
@@ -7763,7 +7795,7 @@
       </c>
       <c r="M115" s="187"/>
     </row>
-    <row r="116" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E116" s="154" t="s">
         <v>117</v>
       </c>
@@ -7778,7 +7810,7 @@
       <c r="L116" s="154"/>
       <c r="M116" s="155"/>
     </row>
-    <row r="117" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E117" s="154"/>
       <c r="F117" s="157"/>
       <c r="G117" s="157"/>
@@ -7789,7 +7821,7 @@
       <c r="L117" s="188"/>
       <c r="M117" s="187"/>
     </row>
-    <row r="118" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E118" s="154" t="s">
         <v>48</v>
       </c>
@@ -7805,7 +7837,7 @@
       <c r="L118" s="154"/>
       <c r="M118" s="155"/>
     </row>
-    <row r="119" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E119" s="164" t="s">
         <v>118</v>
       </c>
@@ -7821,7 +7853,7 @@
       <c r="L119" s="154"/>
       <c r="M119" s="155"/>
     </row>
-    <row r="120" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E120" s="164" t="s">
         <v>122</v>
       </c>
@@ -7837,7 +7869,7 @@
       <c r="L120" s="154"/>
       <c r="M120" s="155"/>
     </row>
-    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E121" s="164"/>
       <c r="F121" s="157"/>
       <c r="G121" s="157"/>
@@ -7848,7 +7880,7 @@
       <c r="L121" s="154"/>
       <c r="M121" s="155"/>
     </row>
-    <row r="122" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E122" s="164"/>
       <c r="F122" s="157"/>
       <c r="G122" s="157"/>
@@ -7859,7 +7891,7 @@
       <c r="L122" s="154"/>
       <c r="M122" s="155"/>
     </row>
-    <row r="123" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F123" s="157"/>
       <c r="G123" s="157"/>
       <c r="H123" s="157"/>
@@ -7869,7 +7901,7 @@
       <c r="L123" s="154"/>
       <c r="M123" s="155"/>
     </row>
-    <row r="124" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E124" s="164"/>
       <c r="F124" s="157"/>
       <c r="G124" s="157"/>
@@ -7880,7 +7912,7 @@
       <c r="L124" s="154"/>
       <c r="M124" s="155"/>
     </row>
-    <row r="125" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E125" s="154"/>
       <c r="F125" s="157"/>
       <c r="G125" s="157"/>
@@ -7891,7 +7923,7 @@
       <c r="L125" s="154"/>
       <c r="M125" s="155"/>
     </row>
-    <row r="126" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E126" s="154"/>
       <c r="F126" s="157"/>
       <c r="G126" s="157"/>
@@ -7902,7 +7934,7 @@
       <c r="L126" s="154"/>
       <c r="M126" s="155"/>
     </row>
-    <row r="127" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E127" s="154"/>
       <c r="F127" s="157"/>
       <c r="G127" s="157"/>
@@ -7913,7 +7945,7 @@
       <c r="L127" s="165"/>
       <c r="M127" s="166"/>
     </row>
-    <row r="128" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E128" s="176" t="s">
         <v>119</v>
       </c>
